--- a/docs/business-case-model_1.xlsx
+++ b/docs/business-case-model_1.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott\Documents\Personal\TraffordConsulting\Clients\MACHAlliance\Agentic_B2B_Order_Intake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB556826-C4B9-4097-8EAD-FCD2122FF439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BF3D34-EF4A-4BE4-B2EE-0691D687E542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26595" yWindow="2115" windowWidth="23700" windowHeight="17865" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27285" yWindow="2805" windowWidth="23700" windowHeight="17865" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
     <sheet name="Sensitivity" sheetId="2" r:id="rId2"/>
     <sheet name="Sources" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -568,131 +565,131 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -777,63 +774,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Model"/>
-      <sheetName val="Sensitivity"/>
-      <sheetName val="Sources"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="B5">
-            <v>500</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>0.02</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>3500</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1024,328 +964,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="18">
         <v>500</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="19">
         <v>12</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="20">
         <v>35</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="21">
         <v>0.02</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="23">
         <f>B5*(B6/60)</f>
         <v>100</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="24">
         <f>B11*B7</f>
         <v>3500</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="25">
         <f>B5*B8</f>
         <v>10</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="15" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="24">
         <f>B13*B9</f>
         <v>0</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="27">
         <f>B12+B14</f>
         <v>3500</v>
       </c>
-      <c r="C15" s="33" t="str">
+      <c r="C15" s="28" t="str">
         <f>"Annual equivalent:  $"&amp;TEXT(B15*12,"#,##0")</f>
         <v>Annual equivalent:  $42,000</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
     </row>
     <row r="18" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="29">
         <v>0.67</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="25">
         <f>B5*B18</f>
         <v>335</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="25">
         <f>B5*(1-B18)</f>
         <v>164.99999999999997</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="36" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="24">
         <f>B21*(B6/60)*B7</f>
         <v>1154.9999999999998</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="24">
         <f>B21*B8*B9</f>
         <v>0</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="27">
         <f>B22+B23</f>
         <v>1154.9999999999998</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="16"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
     </row>
     <row r="27" spans="1:3" ht="36" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="30">
         <v>0</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="37">
+      <c r="B29" s="32">
         <f>B15-B24</f>
         <v>2345</v>
       </c>
-      <c r="C29" s="19"/>
+      <c r="C29" s="16"/>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="32">
         <f>B29*12</f>
         <v>28140</v>
       </c>
-      <c r="C30" s="19"/>
+      <c r="C30" s="16"/>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="38" t="str">
+      <c r="B31" s="33" t="str">
         <f>IF(B27=0,"—",IF(B29&lt;=0,"Does not pay back",TEXT(B27/B29,"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="C31" s="19"/>
+      <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
     </row>
     <row r="34" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
     </row>
     <row r="35" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
     </row>
     <row r="36" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1373,284 +1313,284 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <f>Model!B5*0.5</f>
         <v>250</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <f>Model!B5*0.6</f>
         <v>300</v>
       </c>
-      <c r="D5" s="40">
-        <f>[1]Model!B5*0.67</f>
+      <c r="D5" s="35">
+        <f>Model!B5*0.67</f>
         <v>335</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <f>Model!B5*0.75</f>
         <v>375</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <f>Model!B5*0.8</f>
         <v>400</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <f>Model!B5*0.9</f>
         <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <f>Model!B5*(1-0.5)</f>
         <v>250</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <f>Model!B5*(1-0.6)</f>
         <v>200</v>
       </c>
-      <c r="D6" s="40">
-        <f>[1]Model!B5*(1-0.67)</f>
+      <c r="D6" s="35">
+        <f>Model!B5*(1-0.67)</f>
         <v>164.99999999999997</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <f>Model!B5*(1-0.75)</f>
         <v>125</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <f>Model!B5*(1-0.8)</f>
         <v>99.999999999999972</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <f>Model!B5*(1-0.9)</f>
         <v>49.999999999999986</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <f>Model!B5*(1-0.5)*(Model!B6/60)*Model!B7</f>
         <v>1750</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <f>Model!B5*(1-0.6)*(Model!B6/60)*Model!B7</f>
         <v>1400</v>
       </c>
-      <c r="D7" s="41">
-        <f>[1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7</f>
+      <c r="D7" s="36">
+        <f>Model!B5*(1-0.67)*(Model!B6/60)*Model!B7</f>
         <v>1154.9999999999998</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <f>Model!B5*(1-0.75)*(Model!B6/60)*Model!B7</f>
         <v>875</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <f>Model!B5*(1-0.8)*(Model!B6/60)*Model!B7</f>
         <v>699.99999999999989</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <f>Model!B5*(1-0.9)*(Model!B6/60)*Model!B7</f>
         <v>349.99999999999994</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <f>Model!B5*(1-0.5)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <f>Model!B5*(1-0.6)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
-      <c r="D8" s="41">
-        <f>[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9</f>
+      <c r="D8" s="36">
+        <f>Model!B5*(1-0.67)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <f>Model!B5*(1-0.75)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <f>Model!B5*(1-0.8)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <f>Model!B5*(1-0.9)*Model!B8*Model!B9</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <f>Model!B5*(1-0.5)*(Model!B6/60)*Model!B7+Model!B5*(1-0.5)*Model!B8*Model!B9</f>
         <v>1750</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <f>Model!B5*(1-0.6)*(Model!B6/60)*Model!B7+Model!B5*(1-0.6)*Model!B8*Model!B9</f>
         <v>1400</v>
       </c>
-      <c r="D9" s="41">
-        <f>[1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7+[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9</f>
+      <c r="D9" s="36">
+        <f>Model!B5*(1-0.67)*(Model!B6/60)*Model!B7+Model!B5*(1-0.67)*Model!B8*Model!B9</f>
         <v>1154.9999999999998</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <f>Model!B5*(1-0.75)*(Model!B6/60)*Model!B7+Model!B5*(1-0.75)*Model!B8*Model!B9</f>
         <v>875</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <f>Model!B5*(1-0.8)*(Model!B6/60)*Model!B7+Model!B5*(1-0.8)*Model!B8*Model!B9</f>
         <v>699.99999999999989</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
         <f>Model!B5*(1-0.9)*(Model!B6/60)*Model!B7+Model!B5*(1-0.9)*Model!B8*Model!B9</f>
         <v>349.99999999999994</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="8">
         <f>Model!B15-(Model!B5*(1-0.5)*(Model!B6/60)*Model!B7+Model!B5*(1-0.5)*Model!B8*Model!B9)</f>
         <v>1750</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="8">
         <f>Model!B15-(Model!B5*(1-0.6)*(Model!B6/60)*Model!B7+Model!B5*(1-0.6)*Model!B8*Model!B9)</f>
         <v>2100</v>
       </c>
-      <c r="D10" s="41">
-        <f>[1]Model!B15-([1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7+[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9)</f>
+      <c r="D10" s="36">
+        <f>Model!B15-(Model!B5*(1-0.67)*(Model!B6/60)*Model!B7+Model!B5*(1-0.67)*Model!B8*Model!B9)</f>
         <v>2345</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="8">
         <f>Model!B15-(Model!B5*(1-0.75)*(Model!B6/60)*Model!B7+Model!B5*(1-0.75)*Model!B8*Model!B9)</f>
         <v>2625</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="8">
         <f>Model!B15-(Model!B5*(1-0.8)*(Model!B6/60)*Model!B7+Model!B5*(1-0.8)*Model!B8*Model!B9)</f>
         <v>2800</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <f>Model!B15-(Model!B5*(1-0.9)*(Model!B6/60)*Model!B7+Model!B5*(1-0.9)*Model!B8*Model!B9)</f>
         <v>3150</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="8">
         <f>(Model!B15-(Model!B5*(1-0.5)*(Model!B6/60)*Model!B7+Model!B5*(1-0.5)*Model!B8*Model!B9))*12</f>
         <v>21000</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <f>(Model!B15-(Model!B5*(1-0.6)*(Model!B6/60)*Model!B7+Model!B5*(1-0.6)*Model!B8*Model!B9))*12</f>
         <v>25200</v>
       </c>
-      <c r="D11" s="41">
-        <f>([1]Model!B15-([1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7+[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9))*12</f>
+      <c r="D11" s="36">
+        <f>(Model!B15-(Model!B5*(1-0.67)*(Model!B6/60)*Model!B7+Model!B5*(1-0.67)*Model!B8*Model!B9))*12</f>
         <v>28140</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <f>(Model!B15-(Model!B5*(1-0.75)*(Model!B6/60)*Model!B7+Model!B5*(1-0.75)*Model!B8*Model!B9))*12</f>
         <v>31500</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="8">
         <f>(Model!B15-(Model!B5*(1-0.8)*(Model!B6/60)*Model!B7+Model!B5*(1-0.8)*Model!B8*Model!B9))*12</f>
         <v>33600</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <f>(Model!B15-(Model!B5*(1-0.9)*(Model!B6/60)*Model!B7+Model!B5*(1-0.9)*Model!B8*Model!B9))*12</f>
         <v>37800</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="6" t="str">
         <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.5)*(Model!B6/60)*Model!B7+Model!B5*(1-0.5)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.5)*(Model!B6/60)*Model!B7+Model!B5*(1-0.5)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="6" t="str">
         <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.6)*(Model!B6/60)*Model!B7+Model!B5*(1-0.6)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.6)*(Model!B6/60)*Model!B7+Model!B5*(1-0.6)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="D12" s="42" t="str">
-        <f>IF([1]Model!B27=0,"—",IF([1]Model!B15-([1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7+[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9)&lt;=0,"N/A",TEXT([1]Model!B27/([1]Model!B15-([1]Model!B5*(1-0.67)*([1]Model!B6/60)*[1]Model!B7+[1]Model!B5*(1-0.67)*[1]Model!B8*[1]Model!B9)),"0.0")))</f>
+      <c r="D12" s="37" t="str">
+        <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.67)*(Model!B6/60)*Model!B7+Model!B5*(1-0.67)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.67)*(Model!B6/60)*Model!B7+Model!B5*(1-0.67)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="E12" s="8" t="str">
+      <c r="E12" s="6" t="str">
         <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.75)*(Model!B6/60)*Model!B7+Model!B5*(1-0.75)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.75)*(Model!B6/60)*Model!B7+Model!B5*(1-0.75)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="F12" s="8" t="str">
+      <c r="F12" s="6" t="str">
         <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.8)*(Model!B6/60)*Model!B7+Model!B5*(1-0.8)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.8)*(Model!B6/60)*Model!B7+Model!B5*(1-0.8)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
-      <c r="G12" s="8" t="str">
+      <c r="G12" s="6" t="str">
         <f>IF(Model!B27=0,"—",IF(Model!B15-(Model!B5*(1-0.9)*(Model!B6/60)*Model!B7+Model!B5*(1-0.9)*Model!B8*Model!B9)&lt;=0,"N/A",TEXT(Model!B27/(Model!B15-(Model!B5*(1-0.9)*(Model!B6/60)*Model!B7+Model!B5*(1-0.9)*Model!B8*Model!B9)),"0.0")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1677,258 +1617,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
     </row>
     <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>110</v>
       </c>
     </row>
